--- a/public/exports-with-coowners/29189501.xlsx
+++ b/public/exports-with-coowners/29189501.xlsx
@@ -59,7 +59,7 @@
       </c>
       <c r="J1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Areal (m²)</t>
+          <t xml:space="preserve">Opvarmet BBR-areal (m²)</t>
         </is>
       </c>
       <c r="K1" t="inlineStr">
@@ -2029,12 +2029,12 @@
       </c>
       <c r="N27" t="inlineStr">
         <is>
-          <t xml:space="preserve">Gyldigt</t>
+          <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
       <c r="O27" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nej</t>
+          <t xml:space="preserve">Ja</t>
         </is>
       </c>
     </row>
@@ -8314,12 +8314,12 @@
       </c>
       <c r="K111" t="inlineStr">
         <is>
-          <t xml:space="preserve">311299905</t>
+          <t xml:space="preserve">311299913</t>
         </is>
       </c>
       <c r="L111" t="inlineStr">
         <is>
-          <t xml:space="preserve">MOE A/S</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="M111" t="inlineStr">
@@ -8389,12 +8389,12 @@
       </c>
       <c r="K112" t="inlineStr">
         <is>
-          <t xml:space="preserve">311299908</t>
+          <t xml:space="preserve">311299913</t>
         </is>
       </c>
       <c r="L112" t="inlineStr">
         <is>
-          <t xml:space="preserve">MOE A/S</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="M112" t="inlineStr">
@@ -8464,12 +8464,12 @@
       </c>
       <c r="K113" t="inlineStr">
         <is>
-          <t xml:space="preserve">311299910</t>
+          <t xml:space="preserve">311299913</t>
         </is>
       </c>
       <c r="L113" t="inlineStr">
         <is>
-          <t xml:space="preserve">MOE A/S</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="M113" t="inlineStr">

--- a/public/exports-with-coowners/29189501.xlsx
+++ b/public/exports-with-coowners/29189501.xlsx
@@ -8314,12 +8314,12 @@
       </c>
       <c r="K111" t="inlineStr">
         <is>
-          <t xml:space="preserve">311299913</t>
+          <t xml:space="preserve">311299905</t>
         </is>
       </c>
       <c r="L111" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">MOE A/S</t>
         </is>
       </c>
       <c r="M111" t="inlineStr">
@@ -8389,12 +8389,12 @@
       </c>
       <c r="K112" t="inlineStr">
         <is>
-          <t xml:space="preserve">311299913</t>
+          <t xml:space="preserve">311299908</t>
         </is>
       </c>
       <c r="L112" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">MOE A/S</t>
         </is>
       </c>
       <c r="M112" t="inlineStr">
@@ -8464,12 +8464,12 @@
       </c>
       <c r="K113" t="inlineStr">
         <is>
-          <t xml:space="preserve">311299913</t>
+          <t xml:space="preserve">311299910</t>
         </is>
       </c>
       <c r="L113" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">MOE A/S</t>
         </is>
       </c>
       <c r="M113" t="inlineStr">
